--- a/data/all_datasets/REDD/REDD_House6_stats/2026-04-04.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-04-04.xlsx
@@ -9196,7 +9196,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E4" t="n">
